--- a/exodus/csv/colors.xlsx
+++ b/exodus/csv/colors.xlsx
@@ -9,11 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="280" yWindow="1180" windowWidth="28160" windowHeight="15260" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$12</definedName>
+  </definedNames>
   <calcPr calcId="150000" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>#EFB605</t>
   </si>
@@ -56,9 +59,6 @@
     <t>#66489F</t>
   </si>
   <si>
-    <t>Viet Nam', '</t>
-  </si>
-  <si>
     <t>#2074A0</t>
   </si>
   <si>
@@ -68,15 +68,9 @@
     <t>#7EB852</t>
   </si>
   <si>
-    <t xml:space="preserve">Myanmar', </t>
-  </si>
-  <si>
     <t>#AAA9AA</t>
   </si>
   <si>
-    <t>Somalia',</t>
-  </si>
-  <si>
     <t>#5CEAEA</t>
   </si>
   <si>
@@ -90,6 +84,57 @@
   </si>
   <si>
     <t>Afghanistan', '</t>
+  </si>
+  <si>
+    <t>1967-1973</t>
+  </si>
+  <si>
+    <t>1972-78, 1992-94, 1997-2004</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>1984-2016</t>
+  </si>
+  <si>
+    <t>1961-1977</t>
+  </si>
+  <si>
+    <t>1990,1992-2015</t>
+  </si>
+  <si>
+    <t>1983-1987, 1992-1997</t>
+  </si>
+  <si>
+    <t>1978,  1980-88, 1992-2010</t>
+  </si>
+  <si>
+    <t>1991-2015, 2017</t>
+  </si>
+  <si>
+    <t>Wars fought</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>Viet Nam</t>
+  </si>
+  <si>
+    <t>Somalia</t>
   </si>
 </sst>
 </file>
@@ -105,12 +150,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -125,9 +176,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,186 +458,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" t="str">
-        <f>CONCATENATE("'",A1,"'",",")</f>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>CONCATENATE("'",A2,"'",",")</f>
         <v>'#E01A25',</v>
       </c>
-      <c r="D1" t="str">
-        <f>CONCATENATE(C1)</f>
-        <v>'#E01A25',</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f t="shared" ref="C3:C12" si="0">CONCATENATE("'",A3,"'",",")</f>
+        <v>'#2074A0',</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>'#C20049',</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>'#10A66E',</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="str">
-        <f t="shared" ref="C2:C11" si="0">CONCATENATE("'",A2,"'",",")</f>
-        <v>'#2074A0',</v>
-      </c>
-      <c r="D2" t="str">
-        <f>CONCATENATE(D1,C2)</f>
-        <v>'#E01A25','#2074A0',</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" si="0"/>
-        <v>'#C20049',</v>
-      </c>
-      <c r="D3" t="str">
-        <f t="shared" ref="D3:D11" si="1">CONCATENATE(D2,C3)</f>
-        <v>'#E01A25','#2074A0','#C20049',</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>'#991C71',</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>'#10A66E',</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E',</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>'#991C71',</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E','#991C71',</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>'#7EB852',</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>'#EFB605',</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>'#AAA9AA',</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>'#7EB852',</v>
-      </c>
-      <c r="D6" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E','#991C71','#7EB852',</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" t="str">
-        <f t="shared" si="0"/>
-        <v>'#EFB605',</v>
-      </c>
-      <c r="D7" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E','#991C71','#7EB852','#EFB605',</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="str">
-        <f t="shared" si="0"/>
-        <v>'#AAA9AA',</v>
-      </c>
-      <c r="D8" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E','#991C71','#7EB852','#EFB605','#AAA9AA',</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="str">
+      <c r="C10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>'#5CEAEA',</v>
       </c>
-      <c r="D9" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E','#991C71','#7EB852','#EFB605','#AAA9AA','#5CEAEA',</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>'#E58903',</v>
       </c>
-      <c r="D10" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E','#991C71','#7EB852','#EFB605','#AAA9AA','#5CEAEA','#E58903',</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="str">
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>'#66489F',</v>
       </c>
-      <c r="D11" t="str">
-        <f t="shared" si="1"/>
-        <v>'#E01A25','#2074A0','#C20049','#10A66E','#991C71','#7EB852','#EFB605','#AAA9AA','#5CEAEA','#E58903','#66489F',</v>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E12"/>
   <sortState ref="A1:B11">
     <sortCondition ref="B1"/>
   </sortState>
